--- a/assignment3/data/llm_all_predictions.xlsx
+++ b/assignment3/data/llm_all_predictions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0664130-F038-7741-BFDA-963ADB544269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F882C5D-CD0E-AB4B-860F-99BD35237B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>378</v>
       </c>
